--- a/jira_export_2026-06-15.xlsx
+++ b/jira_export_2026-06-15.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>172 €/h</t>
+          <t>171 €/h</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>334.2 h</t>
+          <t>338.0 h</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.8%</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>610.8 h</t>
+          <t>607.0 h</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>4</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L64" s="13" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>207</v>
       </c>
       <c r="P64" s="14" t="n">
-        <v>55.2</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="65">
@@ -9838,7 +9838,7 @@
         <v>8</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>15</v>
       </c>
       <c r="K118" s="13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="13" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>33</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>35066.73</v>
       </c>
       <c r="P151" s="17" t="n">
-        <v>172.34</v>
+        <v>171.07</v>
       </c>
     </row>
   </sheetData>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>217</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="7">
@@ -14096,7 +14096,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>176.25</v>
+        <v>177.75</v>
       </c>
     </row>
     <row r="8">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>16.5</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="13">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>74</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="15">
@@ -14205,13 +14205,13 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>61.75</v>
+        <v>62.25</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>56</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="18">
@@ -14221,13 +14221,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>140</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>-84</v>
+        <v>-82</v>
       </c>
     </row>
     <row r="19">
@@ -14285,13 +14285,13 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>119</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>-87</v>
+        <v>-86.5</v>
       </c>
     </row>
     <row r="23">
@@ -14301,13 +14301,13 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>30.5</v>
+        <v>31.25</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>133</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>-102.5</v>
+        <v>-101.75</v>
       </c>
     </row>
   </sheetData>
@@ -14410,13 +14410,13 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>148.75</v>
+        <v>150.25</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>467.04</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>35.5</v>
@@ -14428,13 +14428,13 @@
         <v>28.5</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>184.25</v>
+        <v>185.75</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>591.58</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
     </row>
   </sheetData>
@@ -14938,11 +14938,11 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>172.34 €</t>
+          <t>171.07 €</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>203.48</v>
+        <v>204.98</v>
       </c>
     </row>
     <row r="25">
@@ -14953,11 +14953,11 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>64.38 €</t>
+          <t>63.76 €</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>153.3</v>
+        <v>154.8</v>
       </c>
     </row>
     <row r="26">
@@ -15684,7 +15684,7 @@
         <v>-72.59999999999999</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>172.34</v>
+        <v>171.07</v>
       </c>
       <c r="J10" s="28" t="n">
         <v>122</v>
@@ -15729,7 +15729,7 @@
         </is>
       </c>
       <c r="I12" s="17" t="n">
-        <v>820.29</v>
+        <v>819.02</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>

--- a/jira_export_2026-06-15.xlsx
+++ b/jira_export_2026-06-15.xlsx
@@ -807,7 +807,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>35,067 €</t>
+          <t>35,469 €</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>9,868 €</t>
+          <t>10,271 €</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.3%</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>171 €/h</t>
+          <t>167 €/h</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>338.0 h</t>
+          <t>348.8 h</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>607.0 h</t>
+          <t>596.2 h</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Paramétrages</t>
+          <t>Clôture</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>895</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>492.25</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT D'ILLE ET VILAINE (CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)] - Purge arrêtés temporaires</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>37620.5</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>11114.25</v>
+        <v>11517</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2787,19 +2787,95 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
           <t>Juin</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B30" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C30" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D30" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E30" s="13" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2830,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P151"/>
+  <dimension ref="A1:P152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3244,7 +3320,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT D'ILLE ET VILAINE (CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -3782,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
@@ -3797,11 +3873,11 @@
       <c r="N16" s="14" t="n">
         <v>895</v>
       </c>
-      <c r="O16" s="15" t="n">
-        <v>492.25</v>
+      <c r="O16" s="14" t="n">
+        <v>895</v>
       </c>
       <c r="P16" s="14" t="n">
-        <v>246.12</v>
+        <v>325.45</v>
       </c>
     </row>
     <row r="17">
@@ -4710,7 +4786,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
@@ -4729,7 +4805,7 @@
         <v>149</v>
       </c>
       <c r="P29" s="11" t="n">
-        <v>298</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="30">
@@ -6134,7 +6210,7 @@
         <v>3</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
@@ -6153,7 +6229,7 @@
         <v>3150</v>
       </c>
       <c r="P49" s="11" t="n">
-        <v>1260</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="50">
@@ -10215,22 +10291,22 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-23410</t>
+          <t>PDMDEP-23521</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+          <t>METROPOLE TOULON- 4 EXPORTS FILIENS</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE]</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E107" s="10" t="n">
@@ -10238,32 +10314,40 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="J107" s="10" t="n">
         <v>11</v>
       </c>
       <c r="K107" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L107" s="10" t="inlineStr"/>
-      <c r="M107" s="10" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L107" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-28054</t>
+        </is>
+      </c>
+      <c r="M107" s="10" t="inlineStr">
+        <is>
+          <t>495929</t>
+        </is>
+      </c>
       <c r="N107" s="11" t="n">
         <v>0</v>
       </c>
@@ -10277,22 +10361,22 @@
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23410</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>[EVREUX PORTES DE NORMANDIE]</t>
         </is>
       </c>
       <c r="E108" s="13" t="n">
@@ -10305,35 +10389,27 @@
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="J108" s="13" t="n">
         <v>11</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" s="13" t="inlineStr">
-        <is>
-          <t>PDMDEP-27570</t>
-        </is>
-      </c>
-      <c r="M108" s="13" t="inlineStr">
-        <is>
-          <t>493613</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L108" s="13" t="inlineStr"/>
+      <c r="M108" s="13" t="inlineStr"/>
       <c r="N108" s="14" t="n">
         <v>0</v>
       </c>
@@ -10347,12 +10423,12 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
@@ -10362,7 +10438,7 @@
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E109" s="10" t="n">
@@ -10385,23 +10461,23 @@
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J109" s="10" t="n">
         <v>11</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N109" s="11" t="n">
@@ -10466,12 +10542,12 @@
       </c>
       <c r="L110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M110" s="13" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N110" s="14" t="n">
@@ -10502,7 +10578,7 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E111" s="10" t="n">
@@ -10536,12 +10612,12 @@
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N111" s="11" t="n">
@@ -10572,7 +10648,7 @@
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E112" s="13" t="n">
@@ -10606,43 +10682,43 @@
       </c>
       <c r="L112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M112" s="13" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N112" s="14" t="n">
-        <v>3121.2</v>
+        <v>0</v>
       </c>
       <c r="O112" s="14" t="n">
-        <v>3121.2</v>
+        <v>0</v>
       </c>
       <c r="P112" s="14" t="n">
-        <v>3567.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E113" s="10" t="n">
@@ -10650,7 +10726,7 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -10660,59 +10736,59 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N113" s="11" t="n">
-        <v>1000</v>
+        <v>3121.2</v>
       </c>
       <c r="O113" s="11" t="n">
-        <v>1930.88</v>
+        <v>3121.2</v>
       </c>
       <c r="P113" s="11" t="n">
-        <v>0</v>
+        <v>3567.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E114" s="13" t="n">
@@ -10720,7 +10796,7 @@
       </c>
       <c r="F114" s="13" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
@@ -10730,35 +10806,35 @@
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J114" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K114" s="13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M114" s="13" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N114" s="14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O114" s="14" t="n">
-        <v>0</v>
+        <v>1930.88</v>
       </c>
       <c r="P114" s="14" t="n">
         <v>0</v>
@@ -10767,22 +10843,22 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E115" s="10" t="n">
@@ -10800,59 +10876,59 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J115" s="10" t="n">
         <v>14</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>1</v>
+        <v>3.25</v>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N115" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="O115" s="15" t="n">
-        <v>250</v>
+        <v>0</v>
+      </c>
+      <c r="O115" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="P115" s="11" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E116" s="13" t="n">
@@ -10875,54 +10951,54 @@
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J116" s="13" t="n">
         <v>14</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M116" s="13" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N116" s="14" t="n">
-        <v>161</v>
-      </c>
-      <c r="O116" s="14" t="n">
-        <v>161</v>
+        <v>500</v>
+      </c>
+      <c r="O116" s="15" t="n">
+        <v>250</v>
       </c>
       <c r="P116" s="14" t="n">
-        <v>107.33</v>
+        <v>250</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-20528</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>[COLOMBES] Nettoyage env Littéralis Expert</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>COLOMBES</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E117" s="10" t="n">
@@ -10938,49 +11014,61 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H117" s="10" t="inlineStr"/>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J117" s="10" t="n">
         <v>14</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L117" s="10" t="inlineStr"/>
-      <c r="M117" s="10" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L117" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M117" s="10" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N117" s="11" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="O117" s="11" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="P117" s="11" t="n">
-        <v>0</v>
+        <v>107.33</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20528</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[COLOMBES] Nettoyage env Littéralis Expert</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>COLOMBES</t>
         </is>
       </c>
       <c r="E118" s="13" t="n">
@@ -10996,32 +11084,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H118" s="13" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H118" s="13" t="inlineStr"/>
       <c r="I118" s="13" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="J118" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K118" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="L118" s="13" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M118" s="13" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+      <c r="L118" s="13" t="inlineStr"/>
+      <c r="M118" s="13" t="inlineStr"/>
       <c r="N118" s="14" t="n">
         <v>0</v>
       </c>
@@ -11035,12 +11111,12 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
@@ -11050,7 +11126,7 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E119" s="10" t="n">
@@ -11068,28 +11144,28 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J119" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K119" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N119" s="11" t="n">
@@ -11105,12 +11181,12 @@
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
@@ -11120,7 +11196,7 @@
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E120" s="13" t="n">
@@ -11138,34 +11214,34 @@
       </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J120" s="13" t="n">
         <v>15</v>
       </c>
       <c r="K120" s="13" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="L120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M120" s="13" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N120" s="14" t="n">
-        <v>702.33</v>
-      </c>
-      <c r="O120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="14" t="n">
@@ -11175,22 +11251,22 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E121" s="10" t="n">
@@ -11213,27 +11289,27 @@
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N121" s="11" t="n">
-        <v>1936</v>
+        <v>702.33</v>
       </c>
       <c r="O121" s="15" t="n">
         <v>0</v>
@@ -11245,22 +11321,22 @@
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E122" s="13" t="n">
@@ -11283,29 +11359,29 @@
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J122" s="13" t="n">
         <v>16</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M122" s="13" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N122" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="14" t="n">
+        <v>1936</v>
+      </c>
+      <c r="O122" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="14" t="n">
@@ -11315,22 +11391,22 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-18687</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>[Andernos les Bains] Paramétrage "vrai" module Terrasses / remplacement Placier déguisé</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>ANDERNOS-LES-BAINS</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E123" s="10" t="n">
@@ -11338,7 +11414,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -11348,28 +11424,28 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>0.5</v>
+        <v>4.75</v>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28022</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>451939</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N123" s="11" t="n">
@@ -11385,12 +11461,12 @@
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-18242</t>
+          <t>PDMDEP-18687</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>[Mont Saint Aignan] Placier Presta : acquisition</t>
+          <t>[Andernos les Bains] Paramétrage "vrai" module Terrasses / remplacement Placier déguisé</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
@@ -11400,7 +11476,7 @@
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>MONT SAINT AIGNAN</t>
+          <t>ANDERNOS-LES-BAINS</t>
         </is>
       </c>
       <c r="E124" s="13" t="n">
@@ -11418,28 +11494,28 @@
       </c>
       <c r="H124" s="13" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="J124" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28021</t>
+          <t>PDMDEP-28022</t>
         </is>
       </c>
       <c r="M124" s="13" t="inlineStr">
         <is>
-          <t>404496</t>
+          <t>451939</t>
         </is>
       </c>
       <c r="N124" s="14" t="n">
@@ -11455,12 +11531,12 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18242</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[Mont Saint Aignan] Placier Presta : acquisition</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -11470,7 +11546,7 @@
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>MONT SAINT AIGNAN</t>
         </is>
       </c>
       <c r="E125" s="10" t="n">
@@ -11483,7 +11559,7 @@
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
@@ -11500,10 +11576,18 @@
         <v>18</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="L125" s="10" t="inlineStr"/>
-      <c r="M125" s="10" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-28021</t>
+        </is>
+      </c>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>404496</t>
+        </is>
+      </c>
       <c r="N125" s="11" t="n">
         <v>0</v>
       </c>
@@ -11517,12 +11601,12 @@
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
@@ -11532,7 +11616,7 @@
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E126" s="13" t="n">
@@ -11545,40 +11629,32 @@
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J126" s="13" t="n">
         <v>18</v>
       </c>
       <c r="K126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="13" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M126" s="13" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>10.25</v>
+      </c>
+      <c r="L126" s="13" t="inlineStr"/>
+      <c r="M126" s="13" t="inlineStr"/>
       <c r="N126" s="14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="O126" s="14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="P126" s="14" t="n">
         <v>0</v>
@@ -11587,22 +11663,22 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E127" s="10" t="n">
@@ -11610,7 +11686,7 @@
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -11620,35 +11696,35 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N127" s="11" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="O127" s="11" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="P127" s="11" t="n">
         <v>0</v>
@@ -11657,12 +11733,12 @@
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-17594</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>[CD 40 LANDES] Param Interfaces + dev spé</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
@@ -11672,7 +11748,7 @@
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>CD 40</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E128" s="13" t="n">
@@ -11695,30 +11771,30 @@
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J128" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K128" s="13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28016</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M128" s="13" t="inlineStr">
         <is>
-          <t>453168</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N128" s="14" t="n">
         <v>0</v>
       </c>
       <c r="O128" s="14" t="n">
-        <v>239.25</v>
+        <v>0</v>
       </c>
       <c r="P128" s="14" t="n">
         <v>0</v>
@@ -11727,12 +11803,12 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-17291</t>
+          <t>PDMDEP-17594</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>[EVREUX] Littéralis Expert</t>
+          <t>[CD 40 LANDES] Param Interfaces + dev spé</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
@@ -11742,7 +11818,7 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>CD 40</t>
         </is>
       </c>
       <c r="E129" s="10" t="n">
@@ -11760,35 +11836,35 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>29/10/2024</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K129" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27496</t>
+          <t>PDMDEP-28016</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>450556</t>
+          <t>453168</t>
         </is>
       </c>
       <c r="N129" s="11" t="n">
         <v>0</v>
       </c>
       <c r="O129" s="11" t="n">
-        <v>1650</v>
+        <v>239.25</v>
       </c>
       <c r="P129" s="11" t="n">
         <v>0</v>
@@ -11797,22 +11873,22 @@
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-17291</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[EVREUX] Littéralis Expert</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E130" s="13" t="n">
@@ -11820,37 +11896,45 @@
       </c>
       <c r="F130" s="13" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="J130" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K130" s="13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L130" s="13" t="inlineStr"/>
-      <c r="M130" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L130" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-27496</t>
+        </is>
+      </c>
+      <c r="M130" s="13" t="inlineStr">
+        <is>
+          <t>450556</t>
+        </is>
+      </c>
       <c r="N130" s="14" t="n">
         <v>0</v>
       </c>
       <c r="O130" s="14" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="P130" s="14" t="n">
         <v>0</v>
@@ -11859,22 +11943,22 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E131" s="10" t="n">
@@ -11882,7 +11966,7 @@
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -11892,19 +11976,19 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L131" s="10" t="inlineStr"/>
       <c r="M131" s="10" t="inlineStr"/>
@@ -11921,22 +12005,22 @@
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E132" s="13" t="n">
@@ -11959,14 +12043,14 @@
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J132" s="13" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="L132" s="13" t="inlineStr"/>
       <c r="M132" s="13" t="inlineStr"/>
@@ -11983,22 +12067,22 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E133" s="10" t="n">
@@ -12016,19 +12100,19 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="L133" s="10" t="inlineStr"/>
       <c r="M133" s="10" t="inlineStr"/>
@@ -12045,22 +12129,22 @@
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E134" s="13" t="n">
@@ -12078,19 +12162,19 @@
       </c>
       <c r="H134" s="13" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J134" s="13" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K134" s="13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L134" s="13" t="inlineStr"/>
       <c r="M134" s="13" t="inlineStr"/>
@@ -12107,12 +12191,12 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
@@ -12122,7 +12206,7 @@
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E135" s="10" t="n">
@@ -12140,19 +12224,19 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
         <v>31</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="10" t="inlineStr"/>
       <c r="M135" s="10" t="inlineStr"/>
@@ -12169,22 +12253,22 @@
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E136" s="13" t="n">
@@ -12207,14 +12291,14 @@
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J136" s="13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K136" s="13" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L136" s="13" t="inlineStr"/>
       <c r="M136" s="13" t="inlineStr"/>
@@ -12231,22 +12315,22 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E137" s="10" t="n">
@@ -12259,35 +12343,27 @@
       </c>
       <c r="G137" s="10" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L137" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M137" s="10" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L137" s="10" t="inlineStr"/>
+      <c r="M137" s="10" t="inlineStr"/>
       <c r="N137" s="11" t="n">
         <v>0</v>
       </c>
@@ -12301,22 +12377,22 @@
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E138" s="13" t="n">
@@ -12329,27 +12405,35 @@
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J138" s="13" t="n">
         <v>33</v>
       </c>
       <c r="K138" s="13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L138" s="13" t="inlineStr"/>
-      <c r="M138" s="13" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="L138" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M138" s="13" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N138" s="14" t="n">
         <v>0</v>
       </c>
@@ -12363,12 +12447,12 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
@@ -12378,7 +12462,7 @@
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E139" s="10" t="n">
@@ -12401,14 +12485,14 @@
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
         <v>33</v>
       </c>
       <c r="K139" s="10" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="L139" s="10" t="inlineStr"/>
       <c r="M139" s="10" t="inlineStr"/>
@@ -12425,28 +12509,26 @@
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E140" s="13" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="n">
+        <v/>
       </c>
       <c r="F140" s="13" t="inlineStr">
         <is>
@@ -12472,7 +12554,7 @@
         <v>33</v>
       </c>
       <c r="K140" s="13" t="n">
-        <v>0.5</v>
+        <v>4.25</v>
       </c>
       <c r="L140" s="13" t="inlineStr"/>
       <c r="M140" s="13" t="inlineStr"/>
@@ -12489,12 +12571,12 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
@@ -12504,12 +12586,12 @@
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -12524,7 +12606,7 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
@@ -12536,7 +12618,7 @@
         <v>33</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L141" s="10" t="inlineStr"/>
       <c r="M141" s="10" t="inlineStr"/>
@@ -12553,23 +12635,27 @@
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C142" s="13" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C142" s="13" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F142" s="13" t="inlineStr">
@@ -12584,19 +12670,19 @@
       </c>
       <c r="H142" s="13" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J142" s="13" t="n">
         <v>33</v>
       </c>
       <c r="K142" s="13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L142" s="13" t="inlineStr"/>
       <c r="M142" s="13" t="inlineStr"/>
@@ -12613,27 +12699,23 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr"/>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -12648,19 +12730,19 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K143" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L143" s="10" t="inlineStr"/>
       <c r="M143" s="10" t="inlineStr"/>
@@ -12677,12 +12759,12 @@
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
         <is>
-          <t>PSC-1278</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
@@ -12692,10 +12774,14 @@
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
-        </is>
-      </c>
-      <c r="E144" s="13" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F144" s="13" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12703,24 +12789,24 @@
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J144" s="13" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K144" s="13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L144" s="13" t="inlineStr"/>
       <c r="M144" s="13" t="inlineStr"/>
@@ -12737,12 +12823,12 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1278</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
@@ -12752,7 +12838,7 @@
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr"/>
@@ -12780,22 +12866,14 @@
         <v>1</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M145" s="10" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L145" s="10" t="inlineStr"/>
+      <c r="M145" s="10" t="inlineStr"/>
       <c r="N145" s="11" t="n">
-        <v>1191.4</v>
-      </c>
-      <c r="O145" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P145" s="11" t="n">
@@ -12805,12 +12883,12 @@
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
@@ -12820,7 +12898,7 @@
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr"/>
@@ -12841,44 +12919,44 @@
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J146" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K146" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33167</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M146" s="13" t="inlineStr">
         <is>
-          <t>00165437</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N146" s="14" t="n">
-        <v>500</v>
+        <v>1191.4</v>
       </c>
       <c r="O146" s="15" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="P146" s="14" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
@@ -12888,7 +12966,7 @@
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr"/>
@@ -12909,44 +12987,44 @@
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32829</t>
+          <t>PDMDEP-33167</t>
         </is>
       </c>
       <c r="M147" s="10" t="inlineStr">
         <is>
-          <t>00163534</t>
+          <t>00165437</t>
         </is>
       </c>
       <c r="N147" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="O147" s="11" t="n">
-        <v>50</v>
+        <v>500</v>
+      </c>
+      <c r="O147" s="15" t="n">
+        <v>250</v>
       </c>
       <c r="P147" s="11" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
@@ -12956,7 +13034,7 @@
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr"/>
@@ -12977,22 +13055,30 @@
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J148" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K148" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" s="13" t="inlineStr"/>
-      <c r="M148" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L148" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M148" s="13" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N148" s="14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O148" s="14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P148" s="14" t="n">
         <v>0</v>
@@ -13001,12 +13087,12 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>PSC-1147</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
@@ -13016,7 +13102,7 @@
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr"/>
@@ -13037,14 +13123,14 @@
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L149" s="10" t="inlineStr"/>
       <c r="M149" s="10" t="inlineStr"/>
@@ -13061,12 +13147,12 @@
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>PSC-1145</t>
+          <t>PSC-1147</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOLBEC</t>
+          <t>Commune de COUTANCES</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
@@ -13074,7 +13160,11 @@
           <t>Remy VINCENT</t>
         </is>
       </c>
-      <c r="D150" s="13" t="inlineStr"/>
+      <c r="D150" s="13" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
       <c r="E150" s="13" t="inlineStr"/>
       <c r="F150" s="13" t="inlineStr">
         <is>
@@ -13100,54 +13190,110 @@
         <v>4</v>
       </c>
       <c r="K150" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="13" t="inlineStr">
+        <v>1.25</v>
+      </c>
+      <c r="L150" s="13" t="inlineStr"/>
+      <c r="M150" s="13" t="inlineStr"/>
+      <c r="N150" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>PSC-1145</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BOLBEC</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr"/>
+      <c r="E151" s="10" t="inlineStr"/>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K151" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="10" t="inlineStr">
         <is>
           <t>PDMDEP-31452</t>
         </is>
       </c>
-      <c r="M150" s="13" t="inlineStr">
+      <c r="M151" s="10" t="inlineStr">
         <is>
           <t>00156409</t>
         </is>
       </c>
-      <c r="N150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="14" t="n">
+      <c r="N151" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="P150" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="16" t="inlineStr">
+      <c r="P151" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B151" s="16" t="inlineStr"/>
-      <c r="C151" s="16" t="inlineStr"/>
-      <c r="D151" s="16" t="inlineStr"/>
-      <c r="E151" s="16" t="inlineStr"/>
-      <c r="F151" s="16" t="inlineStr"/>
-      <c r="G151" s="16" t="inlineStr"/>
-      <c r="H151" s="16" t="inlineStr"/>
-      <c r="I151" s="16" t="inlineStr"/>
-      <c r="J151" s="16" t="inlineStr"/>
-      <c r="K151" s="16" t="inlineStr"/>
-      <c r="L151" s="16" t="inlineStr"/>
-      <c r="M151" s="16" t="inlineStr"/>
-      <c r="N151" s="17" t="n">
+      <c r="B152" s="16" t="inlineStr"/>
+      <c r="C152" s="16" t="inlineStr"/>
+      <c r="D152" s="16" t="inlineStr"/>
+      <c r="E152" s="16" t="inlineStr"/>
+      <c r="F152" s="16" t="inlineStr"/>
+      <c r="G152" s="16" t="inlineStr"/>
+      <c r="H152" s="16" t="inlineStr"/>
+      <c r="I152" s="16" t="inlineStr"/>
+      <c r="J152" s="16" t="inlineStr"/>
+      <c r="K152" s="16" t="inlineStr"/>
+      <c r="L152" s="16" t="inlineStr"/>
+      <c r="M152" s="16" t="inlineStr"/>
+      <c r="N152" s="17" t="n">
         <v>67144.24000000001</v>
       </c>
-      <c r="O151" s="17" t="n">
-        <v>35066.73</v>
-      </c>
-      <c r="P151" s="17" t="n">
-        <v>171.07</v>
+      <c r="O152" s="17" t="n">
+        <v>35469.48</v>
+      </c>
+      <c r="P152" s="17" t="n">
+        <v>166.73</v>
       </c>
     </row>
   </sheetData>
@@ -13299,6 +13445,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14086,7 +14233,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>218.5</v>
+        <v>226.75</v>
       </c>
     </row>
     <row r="7">
@@ -14096,7 +14243,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>177.75</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="8">
@@ -14136,7 +14283,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>33.25</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="12">
@@ -14156,7 +14303,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="14">
@@ -14166,7 +14313,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>76.25</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="15">
@@ -14221,61 +14368,61 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>58</v>
+        <v>59.75</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>140</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>-82</v>
+        <v>-80.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Rémy Vincent</t>
+          <t>Maxime Pontonnier</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
         <v>53.75</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>-58.25</v>
+        <v>-30.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Bérénice Bossard</t>
+          <t>Rémy Vincent</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>50.5</v>
+        <v>53.75</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>-103.5</v>
+        <v>-58.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Maxime Pontonnier</t>
+          <t>Bérénice Bossard</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>49.75</v>
+        <v>53.5</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>-34.25</v>
+        <v>-100.5</v>
       </c>
     </row>
     <row r="22">
@@ -14285,13 +14432,13 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>119</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>-86.5</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="23">
@@ -14301,13 +14448,13 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>31.25</v>
+        <v>32.75</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>133</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>-101.75</v>
+        <v>-100.25</v>
       </c>
     </row>
   </sheetData>
@@ -14410,31 +14557,31 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>150.25</v>
+        <v>154</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>467.04</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>32.2</v>
+        <v>33</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>35.5</v>
+        <v>37</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>124.54</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>28.5</v>
+        <v>29.7</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>185.75</v>
+        <v>191</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>591.58</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>29.8</v>
+        <v>30.7</v>
       </c>
     </row>
   </sheetData>
@@ -14566,13 +14713,13 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>66.5</v>
+        <v>71</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>268.26</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>24.8</v>
+        <v>26.5</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>5.5</v>
@@ -14584,13 +14731,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>72</v>
+        <v>76.5</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>268.26</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>25.5</v>
+        <v>27.1</v>
       </c>
     </row>
   </sheetData>
@@ -14735,7 +14882,7 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
@@ -14754,7 +14901,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14912,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" s="10" t="inlineStr"/>
     </row>
@@ -14817,7 +14964,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>35,066.73 €</t>
+          <t>35,469.48 €</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -14827,7 +14974,7 @@
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -14837,7 +14984,7 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.3%</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14996,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>9,868.10 €</t>
+          <t>10,270.85 €</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -14859,7 +15006,7 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -14869,7 +15016,7 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>-81.4%</t>
+          <t>-80.7%</t>
         </is>
       </c>
     </row>
@@ -14938,11 +15085,11 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>171.07 €</t>
+          <t>166.73 €</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>204.98</v>
+        <v>212.73</v>
       </c>
     </row>
     <row r="25">
@@ -14953,11 +15100,11 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>63.76 €</t>
+          <t>64.79 €</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>154.8</v>
+        <v>158.5</v>
       </c>
     </row>
     <row r="26">
@@ -14968,11 +15115,11 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>520.10 €</t>
+          <t>480.43 €</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>48.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="27"/>
@@ -15016,12 +15163,12 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>26,095.03 €</t>
+          <t>26,497.78 €</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -15038,7 +15185,7 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15303,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -15168,12 +15315,12 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>4,565.90 €</t>
+          <t>4,968.65 €</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -15235,7 +15382,7 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15409,7 @@
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -15289,7 +15436,7 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15463,7 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15490,7 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -15663,10 +15810,10 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>35066.73</v>
+        <v>35469.48</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>9868.1</v>
+        <v>10270.85</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>25198.63</v>
@@ -15675,19 +15822,19 @@
         <v>120460</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="G10" s="29" t="n">
         <v>128013</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>-72.59999999999999</v>
+        <v>-72.3</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>171.07</v>
+        <v>166.73</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K10" s="28" t="n">
         <v>48</v>
@@ -15704,10 +15851,10 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>436996.09</v>
+        <v>437398.84</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>220673.11</v>
+        <v>221075.86</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>216322.98</v>
@@ -15729,7 +15876,7 @@
         </is>
       </c>
       <c r="I12" s="17" t="n">
-        <v>819.02</v>
+        <v>814.6799999999999</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
